--- a/output_files/weekly_analysis.xlsx
+++ b/output_files/weekly_analysis.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="market_trend" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="market_trend" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="screened_stocks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -488,20 +489,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19298.4365</v>
+        <v>19696.6209</v>
       </c>
       <c r="D2" t="n">
-        <v>18526.5734</v>
+        <v>19156.289</v>
       </c>
       <c r="E2" t="n">
-        <v>19206.4886</v>
+        <v>19192.6521</v>
       </c>
       <c r="F2" t="n">
-        <v>18837.1435</v>
+        <v>18837.1433</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,6 +522,810 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>Both weekly and daily EMA-direction checks are rising.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>latest_trade_date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>latest_close</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>all_time_high</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ath_trade_date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>days_since_ath</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pct_below_ath</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ath_category</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>340.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>369.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>108</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>distant_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACMESOLAR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>305.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>221</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>distant_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2395</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2634.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>recent_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ANURAS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1341</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1407</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>71</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ASTERDM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>705.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>732.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>183</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>distant_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1856</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1935.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>49</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>recent_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CANFINHOME</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>909.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>971.5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>119</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>distant_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CRAFTSMAN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7570</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8220</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>80</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>449.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>490</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>171</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>distant_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>293</v>
+      </c>
+      <c r="D11" t="n">
+        <v>302</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GESHIP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1404.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1543.7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>652</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>distant_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>689.45</v>
+      </c>
+      <c r="D13" t="n">
+        <v>721</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2024-08-30</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>602</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>distant_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>JBCHEPHARM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2005.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2195</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>recent_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4816.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5303</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>53</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6452</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6965</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>73</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>89.29000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>703</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>distant_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>262.79</v>
+      </c>
+      <c r="D18" t="n">
+        <v>285.6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>72</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PIRAMALFIN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1863</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1954.5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>95</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>321.4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>64</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SAILIFE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1024.95</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SARDAEN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>581.4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>639.75</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>220</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>distant_ath</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>THELEELA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>429.05</v>
+      </c>
+      <c r="D23" t="n">
+        <v>474.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>275</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>distant_ath</t>
         </is>
       </c>
     </row>

--- a/output_files/weekly_analysis.xlsx
+++ b/output_files/weekly_analysis.xlsx
@@ -489,20 +489,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19696.6209</v>
+        <v>19784.108</v>
       </c>
       <c r="D2" t="n">
-        <v>19156.289</v>
+        <v>19298.4365</v>
       </c>
       <c r="E2" t="n">
-        <v>19192.6521</v>
+        <v>19371.7699</v>
       </c>
       <c r="F2" t="n">
-        <v>18837.1433</v>
+        <v>19043.9081</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -536,46 +536,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>latest_trade_date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>latest_close</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>all_time_high</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ath_trade_date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>days_since_ath</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>squeeze_timeframe</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sqz_on</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sqz_value</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>pct_below_ath</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ath_category</t>
         </is>
@@ -584,32 +599,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>AADHARHFC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>340.6</v>
+        <v>493.25</v>
       </c>
       <c r="D2" t="n">
-        <v>369.3</v>
+        <v>547.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>108</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7.77</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>216</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-5.35832722981771</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>distant_ath</t>
         </is>
@@ -618,100 +644,133 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACMESOLAR</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>305.3</v>
+        <v>1324.6</v>
       </c>
       <c r="D3" t="n">
-        <v>324.3</v>
+        <v>1407</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>221</v>
-      </c>
-      <c r="G3" t="n">
+        <v>75</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.4999999999999982</v>
+      </c>
+      <c r="J3" t="n">
         <v>5.86</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>distant_ath</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>CANFINHOME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2395</v>
+        <v>905.2</v>
       </c>
       <c r="D4" t="n">
-        <v>2634.8</v>
+        <v>971.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
-      </c>
-      <c r="G4" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>recent_ath</t>
+        <v>123</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-56.60834757486979</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>distant_ath</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1341</v>
+        <v>7554.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1407</v>
+        <v>8220</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>71</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>84</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-298.9166666666667</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>midrange_ath</t>
         </is>
@@ -720,610 +779,178 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASTERDM</t>
+          <t>JAINREC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>705.25</v>
+        <v>434.35</v>
       </c>
       <c r="D6" t="n">
-        <v>732.2</v>
+        <v>476.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>183</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>distant_ath</t>
+        <v>27</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>35.91666666666666</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>recent_ath</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1856</v>
+        <v>6600</v>
       </c>
       <c r="D7" t="n">
-        <v>1935.5</v>
+        <v>6965</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>recent_ath</t>
+        <v>77</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>211.5833333333333</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CANFINHOME</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>909.6</v>
+        <v>324</v>
       </c>
       <c r="D8" t="n">
-        <v>971.5</v>
+        <v>340.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>119</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>distant_ath</t>
+        <v>68</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6.508326212565103</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>midrange_ath</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>USHAMART</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7570</v>
+        <v>459.8</v>
       </c>
       <c r="D9" t="n">
-        <v>8220</v>
+        <v>497.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>80</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>midrange_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DELHIVERY</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>449.7</v>
-      </c>
-      <c r="D10" t="n">
-        <v>490</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>171</v>
-      </c>
-      <c r="G10" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>distant_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>293</v>
-      </c>
-      <c r="D11" t="n">
-        <v>302</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>56</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>midrange_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>GESHIP</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1404.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1543.7</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>652</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9.02</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>distant_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>689.45</v>
-      </c>
-      <c r="D13" t="n">
-        <v>721</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2024-08-30</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>602</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>distant_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>JBCHEPHARM</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2005.8</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2195</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>35</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>recent_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>KEI</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4816.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5303</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>53</v>
-      </c>
-      <c r="G15" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>midrange_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NAVINFLUOR</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>6452</v>
-      </c>
-      <c r="D16" t="n">
-        <v>6965</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>73</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>midrange_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NMDC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>89.29000000000001</v>
-      </c>
-      <c r="D17" t="n">
-        <v>95.45</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>703</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>distant_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>262.79</v>
-      </c>
-      <c r="D18" t="n">
-        <v>285.6</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>72</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>midrange_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PIRAMALFIN</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1863</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1954.5</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>95</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>midrange_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>RBLBANK</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>321.4</v>
-      </c>
-      <c r="D20" t="n">
-        <v>340.4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>64</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>midrange_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SAILIFE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1024.95</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1084</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>50</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>midrange_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SARDAEN</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>581.4</v>
-      </c>
-      <c r="D22" t="n">
-        <v>639.75</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>220</v>
-      </c>
-      <c r="G22" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>distant_ath</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>THELEELA</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>429.05</v>
-      </c>
-      <c r="D23" t="n">
-        <v>474.4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>275</v>
-      </c>
-      <c r="G23" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="H23" t="inlineStr">
+        <v>169</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.108327229817707</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>distant_ath</t>
         </is>
